--- a/data/xlsx/pksf--electrical-installation-and-maintenance-construction.xlsx
+++ b/data/xlsx/pksf--electrical-installation-and-maintenance-construction.xlsx
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -132,6 +132,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -503,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="18" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -666,7 +678,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -690,7 +702,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -714,7 +726,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="18" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -738,7 +750,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="18" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -762,7 +774,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -786,7 +798,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="18" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -810,7 +822,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -834,7 +846,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="18" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -858,7 +870,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="18" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -882,7 +894,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="18" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -906,7 +918,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="18" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -930,7 +942,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="18" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -954,7 +966,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="18" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -978,7 +990,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="18" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1002,7 +1014,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="18" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1026,7 +1038,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="18" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1050,7 +1062,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="18" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1074,7 +1086,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="14.15" customHeight="1">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="18" t="n">
         <v>19</v>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -1098,7 +1110,7 @@
       <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="14.15" customHeight="1">
-      <c r="A35" s="14" t="n">
+      <c r="A35" s="18" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -1122,7 +1134,7 @@
       <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="14.15" customHeight="1">
-      <c r="A36" s="14" t="n">
+      <c r="A36" s="18" t="n">
         <v>21</v>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -1146,7 +1158,7 @@
       <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="14.15" customHeight="1">
-      <c r="A37" s="14" t="n">
+      <c r="A37" s="18" t="n">
         <v>22</v>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -1170,7 +1182,7 @@
       <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="14.15" customHeight="1">
-      <c r="A38" s="14" t="n">
+      <c r="A38" s="18" t="n">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -1194,7 +1206,7 @@
       <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1202,18 +1214,18 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="12" t="n"/>
-      <c r="E39" s="15">
+      <c r="E39" s="19">
         <f>SUM(E16:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="19">
         <f>SUM(F16:F38)</f>
         <v/>
       </c>
       <c r="G39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1222,7 +1234,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="15">
+      <c r="F40" s="19">
         <f>F39/E39*100</f>
         <v/>
       </c>
@@ -1230,7 +1242,7 @@
     </row>
     <row r="41" ht="9.75" customHeight="1"/>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1239,23 +1251,31 @@
       <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="15">
+      <c r="F42" s="19">
         <f>F40*30/100</f>
         <v/>
       </c>
-      <c r="G42" s="15" t="inlineStr">
+      <c r="G42" s="19" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
     </row>
+    <row r="43" ht="28.3" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>* For this course, the institute should have at least 15 channel wiring boards/booths and 3 concealed wiring booths. Otherwise, the total points achieved will be halved.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A41:G41"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="A40:E40"/>
